--- a/feedback_forms/020_data_support_evaluation_form--feedback_forms.xlsx
+++ b/feedback_forms/020_data_support_evaluation_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>first_section</t>
+          <t>Initial Contact with Support</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,86 +548,82 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>rating_score</t>
+          <t>Rating Score</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>satisfaction_level</t>
+          <t>areas_for_improvement</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>satisfaction_level</t>
+          <t>Areas for Improvement</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>improvement_areas</t>
+          <t>contact_frequency</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>improvement_areas</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Please select areas where we can improve</t>
-        </is>
-      </c>
+          <t>Contact Frequency</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>basis_for_rating</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>Basis for Rating</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -639,18 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>average_rating</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Average Rating</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -662,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -680,40 +676,40 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>follow_up</t>
+          <t>satisfaction_level</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>follow_up</t>
+          <t>Satisfaction Level</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>team_member_rating</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>Team Member Rating</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -731,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>team_member</t>
+          <t>team_lead_rating</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>team_member</t>
+          <t>Team Lead Rating</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -749,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>team_lead</t>
+          <t>support_team_performance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>team_lead</t>
+          <t>Support Team Performance</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -772,46 +768,46 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>other_comments</t>
+          <t>rating_scale</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>other_comments</t>
+          <t>Rating Scale</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>rating_system</t>
+          <t>rating_score_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>rating_system</t>
+          <t>Rating Score 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -823,363 +819,41 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>rating_frequency</t>
+          <t>rating_scale_type</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>rating_frequency</t>
+          <t>Rating Scale Type</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>rating_basis</t>
+          <t>rating_score_total</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>rating_basis</t>
+          <t>Rating Score Total</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>rating_score_frequency</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>rating_score_frequency</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>rating_scale</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>rating_scale</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>rating_scale_type</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>rating_scale_type</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>rating_score_range</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>rating_score_range</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>rating_score_average</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>rating_score_average</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>rating_score_total</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>rating_score_total</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>other_fields</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>other_fields</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>team_member_notes</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>team_member_notes</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>team_lead_notes</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>team_lead_notes</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1194,12 +868,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1256,442 +930,561 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>satisfaction_level_choices</t>
+          <t>areas_for_improvement_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>satisfaction_level_choices</t>
+          <t>areas_for_improvement_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>response_time</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>Response Time</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>satisfaction_level_choices</t>
+          <t>areas_for_improvement_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>knowledge</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>Knowledge</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>improvement_areas_choices</t>
+          <t>areas_for_improvement_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>problem_solving</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Problem Solving</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>improvement_areas_choices</t>
+          <t>areas_for_improvement_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>overall_experience</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Overall Experience</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>team_member_choices</t>
+          <t>contact_frequency_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>team_member_choices</t>
+          <t>contact_frequency_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>team_member_choices</t>
+          <t>contact_frequency_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>team_lead_choices</t>
+          <t>contact_frequency_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>team_lead_choices</t>
+          <t>basis_for_rating_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>experience</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>Experience</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>team_lead_choices</t>
+          <t>basis_for_rating_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>knowledge</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>Knowledge</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>rating_system_choices</t>
+          <t>basis_for_rating_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>rating_system_choices</t>
+          <t>basis_for_rating_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>response_time</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>Response Time</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>rating_system_choices</t>
+          <t>satisfaction_level_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>rating_frequency_choices</t>
+          <t>satisfaction_level_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>rating_frequency_choices</t>
+          <t>satisfaction_level_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>rating_frequency_choices</t>
+          <t>satisfaction_level_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>rating_basis_choices</t>
+          <t>satisfaction_level_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>rating_basis_choices</t>
+          <t>team_member_rating_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>rating_basis_choices</t>
+          <t>team_member_rating_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>rating_scale_choices</t>
+          <t>team_member_rating_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>rating_scale_choices</t>
+          <t>team_member_rating_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>rating_scale_choices</t>
+          <t>team_member_rating_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>very_bad</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>Very Bad</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>rating_scale_type_choices</t>
+          <t>team_lead_rating_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>rating_scale_type_choices</t>
+          <t>team_lead_rating_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>team_lead_rating_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>team_lead_rating_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Bad</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>team_lead_rating_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>very_bad</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Very Bad</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>rating_scale_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>scale_1-5</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Scale 1-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>rating_scale_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>scale_1-10</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Scale 1-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>rating_scale_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>scale_6-10</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Scale 6-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>rating_scale_type_choices</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>option_3</t>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Linear</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>rating_scale_type_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>non-linear</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Non-Linear</t>
         </is>
       </c>
     </row>
